--- a/artfynd/A 28976-2026 artfynd.xlsx
+++ b/artfynd/A 28976-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,112 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135429737</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sirsjöängen, Sirsjöängen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>470206</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6552430</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28976-2026 artfynd.xlsx
+++ b/artfynd/A 28976-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6995577</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,8 +904,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135429737</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28976-2026 artfynd.xlsx
+++ b/artfynd/A 28976-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>135429737</v>
       </c>
       <c r="B3" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28976-2026 artfynd.xlsx
+++ b/artfynd/A 28976-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,9 +799,121 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135429737</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sirsjöängen, Sirsjöängen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>470206</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6552430</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135429737</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
